--- a/artfynd/A 10529-2025 artfynd.xlsx
+++ b/artfynd/A 10529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4874931</v>
+        <v>280430</v>
       </c>
       <c r="B2" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222467</v>
+        <v>260</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Myrstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Carex heleonastes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>Ehrh. ex L.f.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513686.8924247687</v>
+        <v>513627</v>
       </c>
       <c r="R2" t="n">
-        <v>7004742.187387886</v>
+        <v>7004741</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>1989-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-07-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikstaxruta 19E1e</t>
+          <t>Transportlista</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Myrkant</t>
+          <t>Myr</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4029127</v>
+        <v>2279401</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>219788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513686.8924247687</v>
+        <v>513627</v>
       </c>
       <c r="R3" t="n">
-        <v>7004742.187387886</v>
+        <v>7004741</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,24 +850,14 @@
           <t>1989-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-07-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikstaxruta 19E1e</t>
+          <t>Transportlista</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Myrkant</t>
+          <t>Myr</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,6 +886,220 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4029127</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1,2 km NO Tjärndalstjärn, Ö Lillsjöhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513687</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7004742</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1989-07-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1989-07-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19E1e</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4874931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>1,2 km NO Tjärndalstjärn, Ö Lillsjöhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513687</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7004742</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1989-07-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1989-07-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikstaxruta 19E1e</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Myrkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10529-2025 artfynd.xlsx
+++ b/artfynd/A 10529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/280430</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2279401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4029127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4874931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>